--- a/src/attributions/attributions_ig_traj_393.xlsx
+++ b/src/attributions/attributions_ig_traj_393.xlsx
@@ -1002,25 +1002,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>-0.2863100128990544</v>
+        <v>-0.2971650308233001</v>
       </c>
       <c r="C2" t="n">
         <v>-0</v>
       </c>
       <c r="D2" t="n">
-        <v>0.2133201334348536</v>
+        <v>0.1818198090985499</v>
       </c>
       <c r="E2" t="n">
-        <v>0.04755082793705591</v>
+        <v>0.05410242697737167</v>
       </c>
       <c r="F2" t="n">
         <v>-0</v>
       </c>
       <c r="G2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
         <v>-0</v>
@@ -1029,19 +1029,19 @@
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.1451708320753986</v>
+        <v>-0.2006894010018105</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M2" t="n">
-        <v>0.1966209931567867</v>
+        <v>0.2222857601907779</v>
       </c>
       <c r="N2" t="n">
-        <v>0.06432243057455955</v>
+        <v>0.09926624981929184</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P2" t="n">
         <v>0</v>
@@ -1050,49 +1050,49 @@
         <v>-0</v>
       </c>
       <c r="R2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.1186485803981984</v>
+        <v>-0.08297315665754879</v>
       </c>
       <c r="U2" t="n">
         <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>0.0250382155064337</v>
+        <v>0.02344480824592489</v>
       </c>
       <c r="W2" t="n">
-        <v>-0.0902748685655885</v>
+        <v>-0.01584413357664259</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA2" t="n">
         <v>-0</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AC2" t="n">
-        <v>-0.1873853927661147</v>
+        <v>-0.0564728217686866</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.04247295410310811</v>
+        <v>0.1848183591198231</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.002188345453412685</v>
+        <v>-0.2237971608149984</v>
       </c>
       <c r="AG2" t="n">
         <v>0</v>
@@ -1101,52 +1101,52 @@
         <v>-0</v>
       </c>
       <c r="AI2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AJ2" t="n">
         <v>0</v>
       </c>
       <c r="AK2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AL2" t="n">
-        <v>-0.05531991834783755</v>
+        <v>-0.2014515295613781</v>
       </c>
       <c r="AM2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.1224489366093055</v>
+        <v>0.04774473920533576</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.09385266564295786</v>
+        <v>-0.2857992312831442</v>
       </c>
       <c r="AP2" t="n">
         <v>-0</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AS2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AT2" t="n">
         <v>0</v>
       </c>
       <c r="AU2" t="n">
-        <v>-0.3408634404953833</v>
+        <v>-0.3628642675210207</v>
       </c>
       <c r="AV2" t="n">
         <v>0</v>
       </c>
       <c r="AW2" t="n">
-        <v>0.09435780670925351</v>
+        <v>0.2067822973528761</v>
       </c>
       <c r="AX2" t="n">
-        <v>-0.1357065060119933</v>
+        <v>0.05164805972327523</v>
       </c>
       <c r="AY2" t="n">
         <v>-0</v>
@@ -1158,25 +1158,25 @@
         <v>0</v>
       </c>
       <c r="BB2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BC2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD2" t="n">
-        <v>-0.02130735158760642</v>
+        <v>0.05718842278088258</v>
       </c>
       <c r="BE2" t="n">
         <v>-0</v>
       </c>
       <c r="BF2" t="n">
-        <v>0.10691692870379</v>
+        <v>0.01858986015506581</v>
       </c>
       <c r="BG2" t="n">
-        <v>0.1115316512402055</v>
+        <v>0.06380527641548721</v>
       </c>
       <c r="BH2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BI2" t="n">
         <v>-0</v>
@@ -1188,19 +1188,19 @@
         <v>-0</v>
       </c>
       <c r="BL2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BM2" t="n">
-        <v>-0.01989581221781007</v>
+        <v>0.1338115136796655</v>
       </c>
       <c r="BN2" t="n">
         <v>0</v>
       </c>
       <c r="BO2" t="n">
-        <v>-0.04352387823875869</v>
+        <v>0.08013667862369776</v>
       </c>
       <c r="BP2" t="n">
-        <v>-0.1491800744827627</v>
+        <v>-0.004342902966900433</v>
       </c>
       <c r="BQ2" t="n">
         <v>0</v>
@@ -1218,16 +1218,16 @@
         <v>0</v>
       </c>
       <c r="BV2" t="n">
-        <v>-0.2242800595505715</v>
+        <v>-0.2235736564507388</v>
       </c>
       <c r="BW2" t="n">
         <v>-0</v>
       </c>
       <c r="BX2" t="n">
-        <v>0.0250820416083286</v>
+        <v>0.1075698538480147</v>
       </c>
       <c r="BY2" t="n">
-        <v>-0.07801841424761749</v>
+        <v>0.004492346953838789</v>
       </c>
       <c r="BZ2" t="n">
         <v>-0</v>
@@ -1236,28 +1236,28 @@
         <v>0</v>
       </c>
       <c r="CB2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CC2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CD2" t="n">
         <v>-0</v>
       </c>
       <c r="CE2" t="n">
-        <v>0.1067566751486354</v>
+        <v>0.2337163779709411</v>
       </c>
       <c r="CF2" t="n">
         <v>0</v>
       </c>
       <c r="CG2" t="n">
-        <v>-0.06873313534003245</v>
+        <v>-0.09052562464412231</v>
       </c>
       <c r="CH2" t="n">
-        <v>0.03273939848186054</v>
+        <v>0.004185720487749123</v>
       </c>
       <c r="CI2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CJ2" t="n">
         <v>0</v>
@@ -1272,52 +1272,52 @@
         <v>-0</v>
       </c>
       <c r="CN2" t="n">
-        <v>0.02871274542388554</v>
+        <v>0.1042081394095408</v>
       </c>
       <c r="CO2" t="n">
         <v>0</v>
       </c>
       <c r="CP2" t="n">
-        <v>-0.01483522306845135</v>
+        <v>-0.210363150830022</v>
       </c>
       <c r="CQ2" t="n">
-        <v>0.1664153704993722</v>
+        <v>-0.04778439061769402</v>
       </c>
       <c r="CR2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CS2" t="n">
         <v>0</v>
       </c>
       <c r="CT2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CU2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CV2" t="n">
         <v>0</v>
       </c>
       <c r="CW2" t="n">
-        <v>0.1241482347839563</v>
+        <v>0.2487562970525398</v>
       </c>
       <c r="CX2" t="n">
         <v>-0</v>
       </c>
       <c r="CY2" t="n">
-        <v>-0.08542116980127948</v>
+        <v>-0.09557848758854319</v>
       </c>
       <c r="CZ2" t="n">
-        <v>0.01513049569149055</v>
+        <v>-0.03084616398342448</v>
       </c>
       <c r="DA2" t="n">
         <v>-0</v>
       </c>
       <c r="DB2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DC2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DD2" t="n">
         <v>-0</v>
@@ -1326,16 +1326,16 @@
         <v>-0</v>
       </c>
       <c r="DF2" t="n">
-        <v>0.08693634870318645</v>
+        <v>0.06236293814206664</v>
       </c>
       <c r="DG2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH2" t="n">
-        <v>-0.0305434957559237</v>
+        <v>-0.08148005362980305</v>
       </c>
       <c r="DI2" t="n">
-        <v>0.06706682701348791</v>
+        <v>-0.0117762082764467</v>
       </c>
       <c r="DJ2" t="n">
         <v>0</v>
@@ -1347,31 +1347,31 @@
         <v>-0</v>
       </c>
       <c r="DM2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DN2" t="n">
         <v>-0</v>
       </c>
       <c r="DO2" t="n">
-        <v>0.05598696861826048</v>
+        <v>0.1265204098512711</v>
       </c>
       <c r="DP2" t="n">
         <v>0</v>
       </c>
       <c r="DQ2" t="n">
-        <v>0.07479269364563712</v>
+        <v>-0.07098071128831125</v>
       </c>
       <c r="DR2" t="n">
-        <v>0.08710614611628299</v>
+        <v>0.07099696702317687</v>
       </c>
       <c r="DS2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DT2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DU2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DV2" t="n">
         <v>-0</v>
@@ -1380,43 +1380,43 @@
         <v>0</v>
       </c>
       <c r="DX2" t="n">
-        <v>0.1661501300566568</v>
+        <v>0.07335525005293494</v>
       </c>
       <c r="DY2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DZ2" t="n">
-        <v>-0.09942967034937744</v>
+        <v>-0.01614658899886435</v>
       </c>
       <c r="EA2" t="n">
-        <v>0.02354411980690037</v>
+        <v>0.02911943501363844</v>
       </c>
       <c r="EB2" t="n">
         <v>0</v>
       </c>
       <c r="EC2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ED2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EE2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EF2" t="n">
         <v>-0</v>
       </c>
       <c r="EG2" t="n">
-        <v>0.06707359706974877</v>
+        <v>0.2696761599764901</v>
       </c>
       <c r="EH2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI2" t="n">
-        <v>-0.04410967305865</v>
+        <v>-0.08521265244672069</v>
       </c>
       <c r="EJ2" t="n">
-        <v>-0.109145757026236</v>
+        <v>-0.05472197271641981</v>
       </c>
       <c r="EK2" t="n">
         <v>-0</v>
@@ -1425,7 +1425,7 @@
         <v>0</v>
       </c>
       <c r="EM2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EN2" t="n">
         <v>0</v>
@@ -1434,25 +1434,25 @@
         <v>-0</v>
       </c>
       <c r="EP2" t="n">
-        <v>-0.05829380938958553</v>
+        <v>-0.115102953424247</v>
       </c>
       <c r="EQ2" t="n">
         <v>0</v>
       </c>
       <c r="ER2" t="n">
-        <v>-0.028652632231917</v>
+        <v>-0.0288677277650115</v>
       </c>
       <c r="ES2" t="n">
-        <v>0.006446421013648177</v>
+        <v>0.020271637700971</v>
       </c>
       <c r="ET2" t="n">
         <v>-0</v>
       </c>
       <c r="EU2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EV2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW2" t="n">
         <v>0</v>
@@ -1461,43 +1461,43 @@
         <v>-0</v>
       </c>
       <c r="EY2" t="n">
-        <v>0.1319830125206858</v>
+        <v>0.2769919289844001</v>
       </c>
       <c r="EZ2" t="n">
         <v>0</v>
       </c>
       <c r="FA2" t="n">
-        <v>-0.06122067637897982</v>
+        <v>-0.1142899461342601</v>
       </c>
       <c r="FB2" t="n">
-        <v>0.0213871901237652</v>
+        <v>0.007971074727111612</v>
       </c>
       <c r="FC2" t="n">
         <v>0</v>
       </c>
       <c r="FD2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FE2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FF2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FG2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FH2" t="n">
-        <v>0.01723630639689141</v>
+        <v>0.1032267711506417</v>
       </c>
       <c r="FI2" t="n">
         <v>0</v>
       </c>
       <c r="FJ2" t="n">
-        <v>0.08307432167051079</v>
+        <v>0.07853395766005737</v>
       </c>
       <c r="FK2" t="n">
-        <v>-0.002805362743190397</v>
+        <v>0.03736541058219419</v>
       </c>
       <c r="FL2" t="n">
         <v>0</v>
@@ -1506,61 +1506,61 @@
         <v>0</v>
       </c>
       <c r="FN2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FP2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ2" t="n">
-        <v>-0.0195540940660355</v>
+        <v>0.2201768536611191</v>
       </c>
       <c r="FR2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS2" t="n">
-        <v>0.1688027560774409</v>
+        <v>0.09534811884716951</v>
       </c>
       <c r="FT2" t="n">
-        <v>0.08341477322545131</v>
+        <v>-0.1081273455646064</v>
       </c>
       <c r="FU2" t="n">
         <v>0</v>
       </c>
       <c r="FV2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX2" t="n">
         <v>-0</v>
       </c>
       <c r="FY2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FZ2" t="n">
-        <v>0.05687568459736464</v>
+        <v>0.2236413714961765</v>
       </c>
       <c r="GA2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GB2" t="n">
-        <v>0.0537403941620035</v>
+        <v>-0.02742113220961006</v>
       </c>
       <c r="GC2" t="n">
         <v>-0</v>
       </c>
       <c r="GD2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GE2" t="n">
         <v>0</v>
       </c>
       <c r="GF2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GG2" t="n">
         <v>0</v>
@@ -1571,7 +1571,7 @@
         <v>0</v>
       </c>
       <c r="B3" t="n">
-        <v>0.07765375748675209</v>
+        <v>0.2456871736245609</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
@@ -1580,52 +1580,52 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.03381584870234718</v>
+        <v>-0.009906475851585789</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.07293840965262915</v>
+        <v>-0.1869444629537565</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K3" t="n">
-        <v>0.04986333522709423</v>
+        <v>0.2516263771506005</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.01966590730516112</v>
+        <v>-0.07598175652375523</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.02977464002243693</v>
+        <v>-0.1082337041005795</v>
       </c>
       <c r="P3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T3" t="n">
-        <v>0.005932941801855291</v>
+        <v>0.09210842019328142</v>
       </c>
       <c r="U3" t="n">
         <v>0</v>
@@ -1634,37 +1634,37 @@
         <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.01865602705222668</v>
+        <v>-0.1203157520910141</v>
       </c>
       <c r="X3" t="n">
-        <v>0.01695638192156892</v>
+        <v>-0.02016131277181833</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA3" t="n">
         <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>-0.0175034483195124</v>
+        <v>-0.05412839188037524</v>
       </c>
       <c r="AD3" t="n">
         <v>-0</v>
       </c>
       <c r="AE3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.001165830608132391</v>
+        <v>-0.2123400635390488</v>
       </c>
       <c r="AG3" t="n">
-        <v>-0.002820146082738788</v>
+        <v>0.04689767835704659</v>
       </c>
       <c r="AH3" t="n">
         <v>-0</v>
@@ -1676,28 +1676,28 @@
         <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL3" t="n">
-        <v>0.01276122348519129</v>
+        <v>0.03160497235881448</v>
       </c>
       <c r="AM3" t="n">
         <v>-0</v>
       </c>
       <c r="AN3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AO3" t="n">
-        <v>-0.01607088431089008</v>
+        <v>-0.05941030717650818</v>
       </c>
       <c r="AP3" t="n">
-        <v>-0.002190039033144834</v>
+        <v>1.197393546260993e-05</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS3" t="n">
         <v>0</v>
@@ -1706,7 +1706,7 @@
         <v>0</v>
       </c>
       <c r="AU3" t="n">
-        <v>0.0782453827328773</v>
+        <v>0.3450599454833746</v>
       </c>
       <c r="AV3" t="n">
         <v>-0</v>
@@ -1715,16 +1715,16 @@
         <v>0</v>
       </c>
       <c r="AX3" t="n">
-        <v>-0.03665641400892343</v>
+        <v>-0.2375302030443718</v>
       </c>
       <c r="AY3" t="n">
-        <v>-0.03539139247904005</v>
+        <v>-0.2029183011741577</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BB3" t="n">
         <v>0</v>
@@ -1733,22 +1733,22 @@
         <v>0</v>
       </c>
       <c r="BD3" t="n">
-        <v>0.02471757684158168</v>
+        <v>0.002698499456687612</v>
       </c>
       <c r="BE3" t="n">
         <v>0</v>
       </c>
       <c r="BF3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BG3" t="n">
-        <v>-0.02063082673580439</v>
+        <v>0.003992614376810577</v>
       </c>
       <c r="BH3" t="n">
-        <v>-0.04040413607848737</v>
+        <v>-0.04724916282861816</v>
       </c>
       <c r="BI3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ3" t="n">
         <v>-0</v>
@@ -1757,25 +1757,25 @@
         <v>0</v>
       </c>
       <c r="BL3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.03594746034721895</v>
+        <v>0.04049182270181427</v>
       </c>
       <c r="BN3" t="n">
         <v>-0</v>
       </c>
       <c r="BO3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BP3" t="n">
-        <v>0.01059732057885673</v>
+        <v>0.09452199187472908</v>
       </c>
       <c r="BQ3" t="n">
-        <v>0.01969491415221181</v>
+        <v>0.03317413892224483</v>
       </c>
       <c r="BR3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS3" t="n">
         <v>-0</v>
@@ -1784,10 +1784,10 @@
         <v>0</v>
       </c>
       <c r="BU3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BV3" t="n">
-        <v>0.03311572028107924</v>
+        <v>0.1618514636756242</v>
       </c>
       <c r="BW3" t="n">
         <v>0</v>
@@ -1796,52 +1796,52 @@
         <v>0</v>
       </c>
       <c r="BY3" t="n">
-        <v>-0.01618496075657468</v>
+        <v>-0.0510484457577945</v>
       </c>
       <c r="BZ3" t="n">
-        <v>-0.003593942604964062</v>
+        <v>-0.08502985356772917</v>
       </c>
       <c r="CA3" t="n">
         <v>-0</v>
       </c>
       <c r="CB3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CC3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE3" t="n">
-        <v>-0.01193330113548456</v>
+        <v>-0.09114136777478667</v>
       </c>
       <c r="CF3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CH3" t="n">
-        <v>0.004076498108803852</v>
+        <v>0.01148397819053023</v>
       </c>
       <c r="CI3" t="n">
-        <v>0.02630448334107258</v>
+        <v>0.09286682439298281</v>
       </c>
       <c r="CJ3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CL3" t="n">
         <v>0</v>
       </c>
       <c r="CM3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CN3" t="n">
-        <v>-0.007219613809401402</v>
+        <v>-0.07306316976944455</v>
       </c>
       <c r="CO3" t="n">
         <v>-0</v>
@@ -1850,25 +1850,25 @@
         <v>-0</v>
       </c>
       <c r="CQ3" t="n">
-        <v>0.0124288736427135</v>
+        <v>0.1232688466570814</v>
       </c>
       <c r="CR3" t="n">
-        <v>-0.006379334348473016</v>
+        <v>0.1213182306852151</v>
       </c>
       <c r="CS3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW3" t="n">
-        <v>-0.007946609763574149</v>
+        <v>-0.08793292866337216</v>
       </c>
       <c r="CX3" t="n">
         <v>0</v>
@@ -1877,145 +1877,145 @@
         <v>0</v>
       </c>
       <c r="CZ3" t="n">
-        <v>0.003721781562089488</v>
+        <v>0.01022493283325212</v>
       </c>
       <c r="DA3" t="n">
-        <v>0.02996893333205113</v>
+        <v>0.1145411111104933</v>
       </c>
       <c r="DB3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC3" t="n">
         <v>0</v>
       </c>
       <c r="DD3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DE3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DF3" t="n">
-        <v>-0.01550332924764262</v>
+        <v>-0.0719948216586552</v>
       </c>
       <c r="DG3" t="n">
         <v>-0</v>
       </c>
       <c r="DH3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI3" t="n">
-        <v>0.03733762119967905</v>
+        <v>-0.1382980195900224</v>
       </c>
       <c r="DJ3" t="n">
-        <v>-0.003238897786757371</v>
+        <v>0.03192060650089487</v>
       </c>
       <c r="DK3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL3" t="n">
         <v>-0</v>
       </c>
       <c r="DM3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN3" t="n">
         <v>-0</v>
       </c>
       <c r="DO3" t="n">
-        <v>0.003866800527031861</v>
+        <v>0.004447777864040109</v>
       </c>
       <c r="DP3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR3" t="n">
-        <v>0.01227749581872184</v>
+        <v>-0.06631764006187241</v>
       </c>
       <c r="DS3" t="n">
-        <v>-0.008743543908462322</v>
+        <v>0.03395772744362772</v>
       </c>
       <c r="DT3" t="n">
         <v>-0</v>
       </c>
       <c r="DU3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DX3" t="n">
-        <v>-0.03709168227646517</v>
+        <v>-0.02494930997492138</v>
       </c>
       <c r="DY3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DZ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA3" t="n">
-        <v>0.0114343880215613</v>
+        <v>-0.0306289833096705</v>
       </c>
       <c r="EB3" t="n">
-        <v>0.01330529770085764</v>
+        <v>0.07057065438860588</v>
       </c>
       <c r="EC3" t="n">
         <v>-0</v>
       </c>
       <c r="ED3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE3" t="n">
         <v>-0</v>
       </c>
       <c r="EF3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG3" t="n">
-        <v>-0.01578067291900693</v>
+        <v>-0.04748738307498086</v>
       </c>
       <c r="EH3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ3" t="n">
-        <v>-0.008884210131924209</v>
+        <v>0.0001025423350785197</v>
       </c>
       <c r="EK3" t="n">
-        <v>0.03240917963538711</v>
+        <v>0.02763962114216909</v>
       </c>
       <c r="EL3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM3" t="n">
         <v>-0</v>
       </c>
       <c r="EN3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EO3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP3" t="n">
-        <v>0.00745529700060979</v>
+        <v>-0.02807184357818664</v>
       </c>
       <c r="EQ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ES3" t="n">
-        <v>0.01605465986306014</v>
+        <v>0.007429663037412913</v>
       </c>
       <c r="ET3" t="n">
-        <v>0.008751549501735453</v>
+        <v>0.1286154893448506</v>
       </c>
       <c r="EU3" t="n">
         <v>0</v>
@@ -2024,25 +2024,25 @@
         <v>0</v>
       </c>
       <c r="EW3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY3" t="n">
-        <v>-0.007811115199668917</v>
+        <v>-0.1017108710291757</v>
       </c>
       <c r="EZ3" t="n">
         <v>-0</v>
       </c>
       <c r="FA3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FB3" t="n">
-        <v>0.007912314425285161</v>
+        <v>-0.01209321166366246</v>
       </c>
       <c r="FC3" t="n">
-        <v>0.03170382617256716</v>
+        <v>0.0828192293630188</v>
       </c>
       <c r="FD3" t="n">
         <v>0</v>
@@ -2051,13 +2051,13 @@
         <v>-0</v>
       </c>
       <c r="FF3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FG3" t="n">
         <v>0</v>
       </c>
       <c r="FH3" t="n">
-        <v>-0.0171695282290082</v>
+        <v>0.1390534467723774</v>
       </c>
       <c r="FI3" t="n">
         <v>-0</v>
@@ -2066,16 +2066,16 @@
         <v>-0</v>
       </c>
       <c r="FK3" t="n">
-        <v>0.00395739883748293</v>
+        <v>-0.04094352960108411</v>
       </c>
       <c r="FL3" t="n">
-        <v>0.01381273725291675</v>
+        <v>0.1184945420611084</v>
       </c>
       <c r="FM3" t="n">
         <v>0</v>
       </c>
       <c r="FN3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO3" t="n">
         <v>0</v>
@@ -2084,7 +2084,7 @@
         <v>0</v>
       </c>
       <c r="FQ3" t="n">
-        <v>0.003794180299352322</v>
+        <v>0.02183729493897992</v>
       </c>
       <c r="FR3" t="n">
         <v>0</v>
@@ -2093,25 +2093,25 @@
         <v>-0</v>
       </c>
       <c r="FT3" t="n">
-        <v>-0.02278959392990534</v>
+        <v>-0.06996609543549577</v>
       </c>
       <c r="FU3" t="n">
-        <v>0.0168766185852211</v>
+        <v>-0.0750104899221139</v>
       </c>
       <c r="FV3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FW3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ3" t="n">
-        <v>0.002078161363450705</v>
+        <v>-0.02762976599244982</v>
       </c>
       <c r="GA3" t="n">
         <v>0</v>
@@ -2123,10 +2123,10 @@
         <v>-0</v>
       </c>
       <c r="GD3" t="n">
-        <v>-0.003552692992910399</v>
+        <v>0.108497708480503</v>
       </c>
       <c r="GE3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF3" t="n">
         <v>-0</v>
@@ -2140,25 +2140,25 @@
         <v>-0</v>
       </c>
       <c r="B4" t="n">
-        <v>-0.4487608613302951</v>
+        <v>-0.5653336278376206</v>
       </c>
       <c r="C4" t="n">
         <v>-0</v>
       </c>
       <c r="D4" t="n">
-        <v>0.3121144184200223</v>
+        <v>0.5915739949721056</v>
       </c>
       <c r="E4" t="n">
-        <v>0.06709626703949123</v>
+        <v>0.0574134921835746</v>
       </c>
       <c r="F4" t="n">
         <v>-0</v>
       </c>
       <c r="G4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
         <v>-0</v>
@@ -2167,22 +2167,22 @@
         <v>-0</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.2202270733415198</v>
+        <v>-0.3845707736905924</v>
       </c>
       <c r="L4" t="n">
         <v>-0</v>
       </c>
       <c r="M4" t="n">
-        <v>0.2601088863268491</v>
+        <v>0.5797804133086653</v>
       </c>
       <c r="N4" t="n">
-        <v>0.01246026550237919</v>
+        <v>0.05609431849481205</v>
       </c>
       <c r="O4" t="n">
         <v>-0</v>
       </c>
       <c r="P4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
         <v>-0</v>
@@ -2194,70 +2194,70 @@
         <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.1575451481189596</v>
+        <v>-0.02604553773806734</v>
       </c>
       <c r="U4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>0.06274923858708903</v>
+        <v>0.09022065948355806</v>
       </c>
       <c r="W4" t="n">
-        <v>0.01010989131183984</v>
+        <v>0.1234475985483632</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Y4" t="n">
         <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
         <v>-0</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AC4" t="n">
-        <v>-0.1828961434636872</v>
+        <v>-0.003972791202407949</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AE4" t="n">
-        <v>-0.07959574710487569</v>
+        <v>0.1645361654234439</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.003775698286657159</v>
+        <v>-0.07547648687381249</v>
       </c>
       <c r="AG4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AI4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AJ4" t="n">
         <v>-0</v>
       </c>
       <c r="AK4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AL4" t="n">
-        <v>-0.1128029439136068</v>
+        <v>-0.2939807223958998</v>
       </c>
       <c r="AM4" t="n">
         <v>-0</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.09507113773672389</v>
+        <v>0.1056842873104513</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.1042474452039632</v>
+        <v>-0.195786746425937</v>
       </c>
       <c r="AP4" t="n">
         <v>-0</v>
@@ -2266,7 +2266,7 @@
         <v>-0</v>
       </c>
       <c r="AR4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AS4" t="n">
         <v>-0</v>
@@ -2275,16 +2275,16 @@
         <v>0</v>
       </c>
       <c r="AU4" t="n">
-        <v>-0.4841684191827451</v>
+        <v>-0.6281137688929105</v>
       </c>
       <c r="AV4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.2502529482308921</v>
+        <v>0.3818556447222284</v>
       </c>
       <c r="AX4" t="n">
-        <v>0.02443177229480079</v>
+        <v>0.3231452846480101</v>
       </c>
       <c r="AY4" t="n">
         <v>-0</v>
@@ -2296,22 +2296,22 @@
         <v>-0</v>
       </c>
       <c r="BB4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BC4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BD4" t="n">
-        <v>-0.04318792240872891</v>
+        <v>0.0008815708986692116</v>
       </c>
       <c r="BE4" t="n">
         <v>-0</v>
       </c>
       <c r="BF4" t="n">
-        <v>0.01434386656345922</v>
+        <v>0.02158226836643909</v>
       </c>
       <c r="BG4" t="n">
-        <v>0.1235938994074157</v>
+        <v>-0.05040433009637475</v>
       </c>
       <c r="BH4" t="n">
         <v>-0</v>
@@ -2329,22 +2329,22 @@
         <v>0</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.01524479988557212</v>
+        <v>0.07139630236887684</v>
       </c>
       <c r="BN4" t="n">
         <v>0</v>
       </c>
       <c r="BO4" t="n">
-        <v>-0.08765741320995507</v>
+        <v>-0.07900834056051668</v>
       </c>
       <c r="BP4" t="n">
-        <v>-0.2307984147900347</v>
+        <v>0.01875790538243734</v>
       </c>
       <c r="BQ4" t="n">
         <v>-0</v>
       </c>
       <c r="BR4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BS4" t="n">
         <v>0</v>
@@ -2353,106 +2353,106 @@
         <v>0</v>
       </c>
       <c r="BU4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BV4" t="n">
-        <v>-0.1307325108404619</v>
+        <v>-0.284548381371478</v>
       </c>
       <c r="BW4" t="n">
         <v>-0</v>
       </c>
       <c r="BX4" t="n">
-        <v>0.138226562245303</v>
+        <v>0.3495683480539087</v>
       </c>
       <c r="BY4" t="n">
-        <v>0.000992649258570471</v>
+        <v>0.02335067841158484</v>
       </c>
       <c r="BZ4" t="n">
         <v>-0</v>
       </c>
       <c r="CA4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CB4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CC4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CD4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE4" t="n">
-        <v>0.1181884322446137</v>
+        <v>0.31567935075035</v>
       </c>
       <c r="CF4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CG4" t="n">
-        <v>-0.0498124435082716</v>
+        <v>-0.2540274154491773</v>
       </c>
       <c r="CH4" t="n">
-        <v>0.02757625280601671</v>
+        <v>-0.0004703905812582194</v>
       </c>
       <c r="CI4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CJ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CK4" t="n">
         <v>-0</v>
       </c>
       <c r="CL4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM4" t="n">
         <v>-0</v>
       </c>
       <c r="CN4" t="n">
-        <v>-0.08896709215885598</v>
+        <v>0.1687290797037603</v>
       </c>
       <c r="CO4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CP4" t="n">
-        <v>0.1525824227985418</v>
+        <v>-0.2822172128501856</v>
       </c>
       <c r="CQ4" t="n">
-        <v>0.09409265210455954</v>
+        <v>-0.07005537953303134</v>
       </c>
       <c r="CR4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CS4" t="n">
         <v>0</v>
       </c>
       <c r="CT4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CU4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CV4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW4" t="n">
-        <v>0.1416073852087246</v>
+        <v>0.3019157242910235</v>
       </c>
       <c r="CX4" t="n">
         <v>-0</v>
       </c>
       <c r="CY4" t="n">
-        <v>-0.07466544061102198</v>
+        <v>-0.2595369445313879</v>
       </c>
       <c r="CZ4" t="n">
-        <v>0.01872735986936323</v>
+        <v>-0.04520232903067972</v>
       </c>
       <c r="DA4" t="n">
         <v>-0</v>
       </c>
       <c r="DB4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DC4" t="n">
         <v>0</v>
@@ -2464,16 +2464,16 @@
         <v>-0</v>
       </c>
       <c r="DF4" t="n">
-        <v>0.004454563806707855</v>
+        <v>0.1223445582236444</v>
       </c>
       <c r="DG4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH4" t="n">
-        <v>-0.01753472260803992</v>
+        <v>0.0307998685764012</v>
       </c>
       <c r="DI4" t="n">
-        <v>-0.1233552557773027</v>
+        <v>0.09052564528081328</v>
       </c>
       <c r="DJ4" t="n">
         <v>0</v>
@@ -2488,25 +2488,25 @@
         <v>-0</v>
       </c>
       <c r="DN4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DO4" t="n">
-        <v>0.04254154429782545</v>
+        <v>0.1217251742842826</v>
       </c>
       <c r="DP4" t="n">
         <v>0</v>
       </c>
       <c r="DQ4" t="n">
-        <v>0.1375610489135267</v>
+        <v>-0.1194186092495757</v>
       </c>
       <c r="DR4" t="n">
-        <v>0.06763706758389545</v>
+        <v>0.02572120728058172</v>
       </c>
       <c r="DS4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DT4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DU4" t="n">
         <v>0</v>
@@ -2518,25 +2518,25 @@
         <v>-0</v>
       </c>
       <c r="DX4" t="n">
-        <v>0.1438760425319049</v>
+        <v>0.1662281728408092</v>
       </c>
       <c r="DY4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DZ4" t="n">
-        <v>0.01665471145554629</v>
+        <v>-0.08529089505004664</v>
       </c>
       <c r="EA4" t="n">
-        <v>0.008791321453108108</v>
+        <v>0.05200795617236262</v>
       </c>
       <c r="EB4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EC4" t="n">
         <v>0</v>
       </c>
       <c r="ED4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EE4" t="n">
         <v>0</v>
@@ -2545,49 +2545,49 @@
         <v>-0</v>
       </c>
       <c r="EG4" t="n">
-        <v>0.07414747419270691</v>
+        <v>0.223432301845017</v>
       </c>
       <c r="EH4" t="n">
         <v>-0</v>
       </c>
       <c r="EI4" t="n">
-        <v>-0.1089494322251175</v>
+        <v>-0.1974289980905875</v>
       </c>
       <c r="EJ4" t="n">
-        <v>-0.05041470911845977</v>
+        <v>-0.08456755871538442</v>
       </c>
       <c r="EK4" t="n">
         <v>0</v>
       </c>
       <c r="EL4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EM4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EN4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO4" t="n">
         <v>0</v>
       </c>
       <c r="EP4" t="n">
-        <v>0.1961983791804812</v>
+        <v>0.2432488067007841</v>
       </c>
       <c r="EQ4" t="n">
         <v>0</v>
       </c>
       <c r="ER4" t="n">
-        <v>0.05000938106430421</v>
+        <v>0.1620817880920348</v>
       </c>
       <c r="ES4" t="n">
-        <v>0.07261004878675251</v>
+        <v>-0.009909559192646369</v>
       </c>
       <c r="ET4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EU4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EV4" t="n">
         <v>-0</v>
@@ -2599,22 +2599,22 @@
         <v>-0</v>
       </c>
       <c r="EY4" t="n">
-        <v>0.1343226184457284</v>
+        <v>0.3224810979491347</v>
       </c>
       <c r="EZ4" t="n">
         <v>0</v>
       </c>
       <c r="FA4" t="n">
-        <v>-0.0535727257066153</v>
+        <v>-0.2977600780223019</v>
       </c>
       <c r="FB4" t="n">
-        <v>0.02479499576352044</v>
+        <v>0.007792723254502459</v>
       </c>
       <c r="FC4" t="n">
         <v>0</v>
       </c>
       <c r="FD4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FE4" t="n">
         <v>-0</v>
@@ -2626,16 +2626,16 @@
         <v>-0</v>
       </c>
       <c r="FH4" t="n">
-        <v>0.09013273324045726</v>
+        <v>-0.08325191142067156</v>
       </c>
       <c r="FI4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FJ4" t="n">
-        <v>-0.103720978546834</v>
+        <v>-0.1862974395021331</v>
       </c>
       <c r="FK4" t="n">
-        <v>0.08195321812306716</v>
+        <v>-0.01852799824383792</v>
       </c>
       <c r="FL4" t="n">
         <v>0</v>
@@ -2647,28 +2647,28 @@
         <v>0</v>
       </c>
       <c r="FO4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FP4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FQ4" t="n">
-        <v>-0.005502177389175796</v>
+        <v>-0.1305008326788906</v>
       </c>
       <c r="FR4" t="n">
         <v>-0</v>
       </c>
       <c r="FS4" t="n">
-        <v>-0.1266948208756934</v>
+        <v>-0.2190880059264356</v>
       </c>
       <c r="FT4" t="n">
-        <v>-0.004993330084177141</v>
+        <v>0.0862137175042256</v>
       </c>
       <c r="FU4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FV4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FW4" t="n">
         <v>0</v>
@@ -2677,31 +2677,31 @@
         <v>-0</v>
       </c>
       <c r="FY4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FZ4" t="n">
-        <v>-0.009398322540494605</v>
+        <v>0.217084636900216</v>
       </c>
       <c r="GA4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GB4" t="n">
-        <v>0.1397099011775991</v>
+        <v>-0.207291893010992</v>
       </c>
       <c r="GC4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GE4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GF4" t="n">
         <v>0</v>
       </c>
       <c r="GG4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="5">
@@ -3278,7 +3278,7 @@
         <v>0</v>
       </c>
       <c r="B6" t="n">
-        <v>0.09779678463455392</v>
+        <v>0.373240002111874</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
@@ -3287,16 +3287,16 @@
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.02776977295578705</v>
+        <v>-0.01241139301014408</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.02707204351872733</v>
+        <v>-0.1873491312551421</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -3305,7 +3305,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0.04232297618606908</v>
+        <v>0.4385653019297592</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -3314,13 +3314,13 @@
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.03163550927198414</v>
+        <v>-0.1132958204492595</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.007603451732893487</v>
+        <v>-0.05357739760936148</v>
       </c>
       <c r="P6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -3329,10 +3329,10 @@
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T6" t="n">
-        <v>0.003369393069613341</v>
+        <v>0.1178691469072105</v>
       </c>
       <c r="U6" t="n">
         <v>-0</v>
@@ -3341,37 +3341,37 @@
         <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.01442950014909297</v>
+        <v>-0.03886516151867565</v>
       </c>
       <c r="X6" t="n">
-        <v>0.02614440514858042</v>
+        <v>0.03114029142500401</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB6" t="n">
         <v>-0</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.0221382465548246</v>
+        <v>-0.007412979736418229</v>
       </c>
       <c r="AD6" t="n">
         <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.03534665982345181</v>
+        <v>-0.2295381556944186</v>
       </c>
       <c r="AG6" t="n">
-        <v>-0.0007498533250204586</v>
+        <v>0.006383491326266985</v>
       </c>
       <c r="AH6" t="n">
         <v>0</v>
@@ -3383,25 +3383,25 @@
         <v>0</v>
       </c>
       <c r="AK6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL6" t="n">
-        <v>0.01313049785327483</v>
+        <v>0.1395552307181151</v>
       </c>
       <c r="AM6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN6" t="n">
         <v>0</v>
       </c>
       <c r="AO6" t="n">
-        <v>-0.01586092621184103</v>
+        <v>-0.01142605165799619</v>
       </c>
       <c r="AP6" t="n">
-        <v>-0.01942785371398706</v>
+        <v>-0.09852309002365335</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR6" t="n">
         <v>-0</v>
@@ -3410,10 +3410,10 @@
         <v>0</v>
       </c>
       <c r="AT6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU6" t="n">
-        <v>0.09196611717072517</v>
+        <v>0.4845288030006384</v>
       </c>
       <c r="AV6" t="n">
         <v>0</v>
@@ -3422,25 +3422,25 @@
         <v>0</v>
       </c>
       <c r="AX6" t="n">
-        <v>-0.01091532453554218</v>
+        <v>-0.263971126221531</v>
       </c>
       <c r="AY6" t="n">
-        <v>-0.0088133769779491</v>
+        <v>-0.1993083666956848</v>
       </c>
       <c r="AZ6" t="n">
         <v>0</v>
       </c>
       <c r="BA6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD6" t="n">
-        <v>0.02066768001248303</v>
+        <v>-0.01681667260043915</v>
       </c>
       <c r="BE6" t="n">
         <v>0</v>
@@ -3449,40 +3449,40 @@
         <v>0</v>
       </c>
       <c r="BG6" t="n">
-        <v>-0.02243116688203153</v>
+        <v>-0.06511160245507391</v>
       </c>
       <c r="BH6" t="n">
-        <v>-0.007360996938176497</v>
+        <v>-0.04618998162292801</v>
       </c>
       <c r="BI6" t="n">
         <v>-0</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK6" t="n">
         <v>0</v>
       </c>
       <c r="BL6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.05177772366975269</v>
+        <v>0.03442072590014718</v>
       </c>
       <c r="BN6" t="n">
         <v>-0</v>
       </c>
       <c r="BO6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BP6" t="n">
-        <v>0.03806377165361665</v>
+        <v>0.104100194859917</v>
       </c>
       <c r="BQ6" t="n">
-        <v>0.01617967543743965</v>
+        <v>0.04830527133929932</v>
       </c>
       <c r="BR6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS6" t="n">
         <v>0</v>
@@ -3494,22 +3494,22 @@
         <v>-0</v>
       </c>
       <c r="BV6" t="n">
-        <v>0.04608476734865451</v>
+        <v>0.3021054141129314</v>
       </c>
       <c r="BW6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX6" t="n">
         <v>0</v>
       </c>
       <c r="BY6" t="n">
-        <v>-0.01678107981471176</v>
+        <v>-0.03964421175090642</v>
       </c>
       <c r="BZ6" t="n">
-        <v>0.02932464660658785</v>
+        <v>-0.07889037555205798</v>
       </c>
       <c r="CA6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB6" t="n">
         <v>-0</v>
@@ -3521,7 +3521,7 @@
         <v>-0</v>
       </c>
       <c r="CE6" t="n">
-        <v>-0.01291273892309817</v>
+        <v>-0.1357832981536787</v>
       </c>
       <c r="CF6" t="n">
         <v>-0</v>
@@ -3530,13 +3530,13 @@
         <v>-0</v>
       </c>
       <c r="CH6" t="n">
-        <v>0.002548015659307606</v>
+        <v>0.02372542748677534</v>
       </c>
       <c r="CI6" t="n">
-        <v>0.01035412295004452</v>
+        <v>0.0895533283902937</v>
       </c>
       <c r="CJ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CK6" t="n">
         <v>0</v>
@@ -3548,103 +3548,103 @@
         <v>0</v>
       </c>
       <c r="CN6" t="n">
-        <v>0.0002742439718239334</v>
+        <v>-0.1833132321672815</v>
       </c>
       <c r="CO6" t="n">
         <v>0</v>
       </c>
       <c r="CP6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ6" t="n">
-        <v>0.002813463887987625</v>
+        <v>0.2417551818705715</v>
       </c>
       <c r="CR6" t="n">
-        <v>-0.03778164998470359</v>
+        <v>0.04693694494903956</v>
       </c>
       <c r="CS6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CU6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV6" t="n">
         <v>0</v>
       </c>
       <c r="CW6" t="n">
-        <v>-0.00674317946677412</v>
+        <v>-0.1258675706314126</v>
       </c>
       <c r="CX6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY6" t="n">
         <v>0</v>
       </c>
       <c r="CZ6" t="n">
-        <v>0.003412990607635664</v>
+        <v>0.009873315875509511</v>
       </c>
       <c r="DA6" t="n">
-        <v>0.01256294856288534</v>
+        <v>0.1002061401199684</v>
       </c>
       <c r="DB6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DC6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD6" t="n">
         <v>0</v>
       </c>
       <c r="DE6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DF6" t="n">
-        <v>-0.01818148957439986</v>
+        <v>-0.08589714341712666</v>
       </c>
       <c r="DG6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI6" t="n">
-        <v>0.03462104369963299</v>
+        <v>-0.08700188582114546</v>
       </c>
       <c r="DJ6" t="n">
-        <v>0.005261321144447573</v>
+        <v>0.08870257728997474</v>
       </c>
       <c r="DK6" t="n">
         <v>0</v>
       </c>
       <c r="DL6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN6" t="n">
         <v>-0</v>
       </c>
       <c r="DO6" t="n">
-        <v>-0.01535655286999584</v>
+        <v>-0.1008426869847492</v>
       </c>
       <c r="DP6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR6" t="n">
-        <v>0.02900346068868937</v>
+        <v>-0.020433399310133</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.00758486525241465</v>
+        <v>0.02085360703967585</v>
       </c>
       <c r="DT6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU6" t="n">
         <v>-0</v>
@@ -3656,103 +3656,103 @@
         <v>-0</v>
       </c>
       <c r="DX6" t="n">
-        <v>-0.01762778729645223</v>
+        <v>0.0530022355940709</v>
       </c>
       <c r="DY6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ6" t="n">
         <v>0</v>
       </c>
       <c r="EA6" t="n">
-        <v>-0.03745796629678676</v>
+        <v>-0.04755664022359285</v>
       </c>
       <c r="EB6" t="n">
-        <v>-0.01561058257182694</v>
+        <v>0.05767142022188213</v>
       </c>
       <c r="EC6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF6" t="n">
         <v>-0</v>
       </c>
       <c r="EG6" t="n">
-        <v>-0.001556450046231629</v>
+        <v>-0.007465237273681942</v>
       </c>
       <c r="EH6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ6" t="n">
-        <v>0.006587477693484734</v>
+        <v>-0.03621552066654996</v>
       </c>
       <c r="EK6" t="n">
-        <v>-0.002211568715968637</v>
+        <v>0.01950902161943761</v>
       </c>
       <c r="EL6" t="n">
         <v>-0</v>
       </c>
       <c r="EM6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EN6" t="n">
         <v>-0</v>
       </c>
       <c r="EO6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP6" t="n">
-        <v>-0.00315756398501371</v>
+        <v>-0.04396774302792601</v>
       </c>
       <c r="EQ6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ER6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ES6" t="n">
-        <v>-0.02472388753054111</v>
+        <v>-0.1501548866820136</v>
       </c>
       <c r="ET6" t="n">
-        <v>-0.04267164733977371</v>
+        <v>-0.1217056384479405</v>
       </c>
       <c r="EU6" t="n">
         <v>-0</v>
       </c>
       <c r="EV6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX6" t="n">
         <v>-0</v>
       </c>
       <c r="EY6" t="n">
-        <v>-0.003129124356926306</v>
+        <v>-0.1506771370337949</v>
       </c>
       <c r="EZ6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FA6" t="n">
         <v>-0</v>
       </c>
       <c r="FB6" t="n">
-        <v>0.001769360760270176</v>
+        <v>-0.0002677009344729085</v>
       </c>
       <c r="FC6" t="n">
-        <v>0.01738247886901063</v>
+        <v>0.07851779187004712</v>
       </c>
       <c r="FD6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FE6" t="n">
         <v>0</v>
@@ -3764,79 +3764,79 @@
         <v>0</v>
       </c>
       <c r="FH6" t="n">
-        <v>-0.0147336029835315</v>
+        <v>-0.1127691322491153</v>
       </c>
       <c r="FI6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ6" t="n">
         <v>-0</v>
       </c>
       <c r="FK6" t="n">
-        <v>-0.03902015357816686</v>
+        <v>0.1347232343452346</v>
       </c>
       <c r="FL6" t="n">
-        <v>0.0009771488481506679</v>
+        <v>0.07936896858937016</v>
       </c>
       <c r="FM6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FN6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO6" t="n">
         <v>0</v>
       </c>
       <c r="FP6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ6" t="n">
-        <v>-0.008874519555491248</v>
+        <v>0.012335489991202</v>
       </c>
       <c r="FR6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS6" t="n">
         <v>-0</v>
       </c>
       <c r="FT6" t="n">
-        <v>-0.01069195566399324</v>
+        <v>-0.06626024785692471</v>
       </c>
       <c r="FU6" t="n">
-        <v>0.01587810262263613</v>
+        <v>-0.06305083770684487</v>
       </c>
       <c r="FV6" t="n">
         <v>-0</v>
       </c>
       <c r="FW6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ6" t="n">
-        <v>-0.02540016764850763</v>
+        <v>-0.03887453421534798</v>
       </c>
       <c r="GA6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB6" t="n">
         <v>-0</v>
       </c>
       <c r="GC6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD6" t="n">
-        <v>-0.01077012974764084</v>
+        <v>0.04490789388486031</v>
       </c>
       <c r="GE6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG6" t="n">
         <v>0</v>
@@ -3847,22 +3847,22 @@
         <v>0</v>
       </c>
       <c r="B7" t="n">
-        <v>0.3055051281798104</v>
+        <v>0.4623483892361979</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.1116883021831919</v>
+        <v>-0.2685835637979603</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.01723889841360684</v>
+        <v>-0.09856367698424701</v>
       </c>
       <c r="F7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H7" t="n">
         <v>-0</v>
@@ -3871,100 +3871,100 @@
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1952144740968712</v>
+        <v>0.4279335792105668</v>
       </c>
       <c r="L7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.09379131448642201</v>
+        <v>-0.2481744631256192</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.07666383166682193</v>
+        <v>-0.1873378223096943</v>
       </c>
       <c r="O7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T7" t="n">
-        <v>0.09959327428864867</v>
+        <v>0.1070078567491835</v>
       </c>
       <c r="U7" t="n">
         <v>-0</v>
       </c>
       <c r="V7" t="n">
-        <v>0.03581302354132411</v>
+        <v>-0.06650527681758647</v>
       </c>
       <c r="W7" t="n">
-        <v>0.04110742599040455</v>
+        <v>-0.1119025978967366</v>
       </c>
       <c r="X7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
         <v>-0</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
         <v>-0</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.1070886115236627</v>
+        <v>-0.06505434863303429</v>
       </c>
       <c r="AD7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>-0.07321152743590241</v>
+        <v>-0.08737282662102884</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.01218465216093521</v>
+        <v>-0.1775957819377167</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL7" t="n">
-        <v>0.003188714218412055</v>
+        <v>0.2229985919410229</v>
       </c>
       <c r="AM7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN7" t="n">
-        <v>-0.03248717906005242</v>
+        <v>-0.1391815568902517</v>
       </c>
       <c r="AO7" t="n">
-        <v>-0.07110965266880069</v>
+        <v>0.06338979601788743</v>
       </c>
       <c r="AP7" t="n">
         <v>0</v>
@@ -3973,52 +3973,52 @@
         <v>0</v>
       </c>
       <c r="AR7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AT7" t="n">
         <v>-0</v>
       </c>
       <c r="AU7" t="n">
-        <v>0.3430581252225197</v>
+        <v>0.4234548566621815</v>
       </c>
       <c r="AV7" t="n">
         <v>-0</v>
       </c>
       <c r="AW7" t="n">
-        <v>0.03451458077763487</v>
+        <v>-0.1899054229211349</v>
       </c>
       <c r="AX7" t="n">
-        <v>0.1690093676683826</v>
+        <v>-0.409452892728837</v>
       </c>
       <c r="AY7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB7" t="n">
         <v>-0</v>
       </c>
       <c r="BC7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BD7" t="n">
-        <v>0.02523415662384805</v>
+        <v>-0.03658187444052814</v>
       </c>
       <c r="BE7" t="n">
         <v>0</v>
       </c>
       <c r="BF7" t="n">
-        <v>-0.06508004869044355</v>
+        <v>-0.03467670438793239</v>
       </c>
       <c r="BG7" t="n">
-        <v>-0.1151261604782218</v>
+        <v>-0.008871478489106537</v>
       </c>
       <c r="BH7" t="n">
         <v>0</v>
@@ -4027,7 +4027,7 @@
         <v>-0</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK7" t="n">
         <v>0</v>
@@ -4036,22 +4036,22 @@
         <v>-0</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.1118626662566837</v>
+        <v>-0.004110613510009405</v>
       </c>
       <c r="BN7" t="n">
         <v>-0</v>
       </c>
       <c r="BO7" t="n">
-        <v>0.0302280187398052</v>
+        <v>0.088421642401755</v>
       </c>
       <c r="BP7" t="n">
-        <v>0.1249398021512294</v>
+        <v>0.03855811973681792</v>
       </c>
       <c r="BQ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS7" t="n">
         <v>-0</v>
@@ -4063,49 +4063,49 @@
         <v>-0</v>
       </c>
       <c r="BV7" t="n">
-        <v>0.1850696570730006</v>
+        <v>0.3437889351327423</v>
       </c>
       <c r="BW7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX7" t="n">
-        <v>0.02855050125360431</v>
+        <v>-0.202421794681634</v>
       </c>
       <c r="BY7" t="n">
-        <v>0.07515669989029142</v>
+        <v>-0.141993253255009</v>
       </c>
       <c r="BZ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD7" t="n">
         <v>-0</v>
       </c>
       <c r="CE7" t="n">
-        <v>-0.06506705711726947</v>
+        <v>-0.1491544150359155</v>
       </c>
       <c r="CF7" t="n">
         <v>-0</v>
       </c>
       <c r="CG7" t="n">
-        <v>0.004552188446947648</v>
+        <v>0.190457264814262</v>
       </c>
       <c r="CH7" t="n">
-        <v>-0.007528580151137815</v>
+        <v>0.03081896412685403</v>
       </c>
       <c r="CI7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK7" t="n">
         <v>0</v>
@@ -4117,22 +4117,22 @@
         <v>0</v>
       </c>
       <c r="CN7" t="n">
-        <v>-0.08100085893450382</v>
+        <v>-0.1337780000822445</v>
       </c>
       <c r="CO7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP7" t="n">
-        <v>-0.09776155780011604</v>
+        <v>0.2888875945107485</v>
       </c>
       <c r="CQ7" t="n">
-        <v>-0.08722633711743664</v>
+        <v>0.2075444033808424</v>
       </c>
       <c r="CR7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT7" t="n">
         <v>-0</v>
@@ -4144,25 +4144,25 @@
         <v>0</v>
       </c>
       <c r="CW7" t="n">
-        <v>-0.04151230558519947</v>
+        <v>-0.1374805607581927</v>
       </c>
       <c r="CX7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY7" t="n">
-        <v>0.02242295272136002</v>
+        <v>0.2132425944029851</v>
       </c>
       <c r="CZ7" t="n">
-        <v>-0.007126341298994118</v>
+        <v>0.04539986699220197</v>
       </c>
       <c r="DA7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DB7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD7" t="n">
         <v>0</v>
@@ -4171,79 +4171,79 @@
         <v>0</v>
       </c>
       <c r="DF7" t="n">
-        <v>-0.07533445224762644</v>
+        <v>-0.1758548982190472</v>
       </c>
       <c r="DG7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH7" t="n">
-        <v>0.005398475260425361</v>
+        <v>0.09603928582185137</v>
       </c>
       <c r="DI7" t="n">
-        <v>0.01310780207539635</v>
+        <v>-0.075607267037247</v>
       </c>
       <c r="DJ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL7" t="n">
         <v>0</v>
       </c>
       <c r="DM7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DN7" t="n">
         <v>-0</v>
       </c>
       <c r="DO7" t="n">
-        <v>-0.06685729876964107</v>
+        <v>-0.07828750152375405</v>
       </c>
       <c r="DP7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ7" t="n">
-        <v>-0.05529298973819896</v>
+        <v>0.09117646373425729</v>
       </c>
       <c r="DR7" t="n">
-        <v>-0.004353121737628815</v>
+        <v>-0.01500838702858775</v>
       </c>
       <c r="DS7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX7" t="n">
-        <v>0.04779914913260182</v>
+        <v>0.05576577535674911</v>
       </c>
       <c r="DY7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ7" t="n">
-        <v>-0.02984062702619616</v>
+        <v>0.05620378027382762</v>
       </c>
       <c r="EA7" t="n">
-        <v>-0.01906504490721115</v>
+        <v>-0.01891762924183479</v>
       </c>
       <c r="EB7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE7" t="n">
         <v>-0</v>
@@ -4252,79 +4252,79 @@
         <v>0</v>
       </c>
       <c r="EG7" t="n">
-        <v>-0.01173152376604417</v>
+        <v>-0.08665306493557669</v>
       </c>
       <c r="EH7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI7" t="n">
-        <v>0.05816418449850169</v>
+        <v>0.1396494921939374</v>
       </c>
       <c r="EJ7" t="n">
-        <v>0.05037182108139945</v>
+        <v>0.04756934736821342</v>
       </c>
       <c r="EK7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EL7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN7" t="n">
         <v>-0</v>
       </c>
       <c r="EO7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP7" t="n">
-        <v>-0.06069537702206312</v>
+        <v>-0.08017397454580959</v>
       </c>
       <c r="EQ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ER7" t="n">
-        <v>-0.05868586201298572</v>
+        <v>-0.1656816795423101</v>
       </c>
       <c r="ES7" t="n">
-        <v>0.006246277827096531</v>
+        <v>-0.03150548087353488</v>
       </c>
       <c r="ET7" t="n">
         <v>-0</v>
       </c>
       <c r="EU7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EW7" t="n">
         <v>-0</v>
       </c>
       <c r="EX7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY7" t="n">
-        <v>-0.05295080906090214</v>
+        <v>-0.1661159293633848</v>
       </c>
       <c r="EZ7" t="n">
         <v>-0</v>
       </c>
       <c r="FA7" t="n">
-        <v>0.01413776130150806</v>
+        <v>0.2149462223555332</v>
       </c>
       <c r="FB7" t="n">
-        <v>0.009042033872069763</v>
+        <v>0.02742791652649283</v>
       </c>
       <c r="FC7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FD7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF7" t="n">
         <v>-0</v>
@@ -4333,49 +4333,49 @@
         <v>-0</v>
       </c>
       <c r="FH7" t="n">
-        <v>0.05551628506402375</v>
+        <v>-0.09353290196931417</v>
       </c>
       <c r="FI7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FJ7" t="n">
-        <v>0.03055216413442334</v>
+        <v>0.1206606166152953</v>
       </c>
       <c r="FK7" t="n">
-        <v>-0.0379126559725626</v>
+        <v>0.01379715418082787</v>
       </c>
       <c r="FL7" t="n">
         <v>-0</v>
       </c>
       <c r="FM7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FN7" t="n">
         <v>0</v>
       </c>
       <c r="FO7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ7" t="n">
-        <v>-0.0227710448248353</v>
+        <v>0.01562189498530546</v>
       </c>
       <c r="FR7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS7" t="n">
-        <v>-0.02548159704748207</v>
+        <v>0.1783145200876754</v>
       </c>
       <c r="FT7" t="n">
-        <v>0.04315243817070006</v>
+        <v>-0.04237750758367725</v>
       </c>
       <c r="FU7" t="n">
         <v>0</v>
       </c>
       <c r="FV7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW7" t="n">
         <v>0</v>
@@ -4384,28 +4384,28 @@
         <v>0</v>
       </c>
       <c r="FY7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ7" t="n">
-        <v>-0.02558426529789555</v>
+        <v>-0.09991614101752636</v>
       </c>
       <c r="GA7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB7" t="n">
-        <v>-0.05279605994794003</v>
+        <v>0.1117619295292324</v>
       </c>
       <c r="GC7" t="n">
         <v>0</v>
       </c>
       <c r="GD7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG7" t="n">
         <v>0</v>
@@ -4985,43 +4985,43 @@
         <v>-0</v>
       </c>
       <c r="B9" t="n">
-        <v>0.2958635253427703</v>
+        <v>0.1302941946911158</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.05065203317901796</v>
+        <v>-0.05964383014383931</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.06387709220629052</v>
+        <v>-0.07850691322066086</v>
       </c>
       <c r="F9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H9" t="n">
         <v>-0</v>
       </c>
       <c r="I9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
         <v>-0</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1759191739902106</v>
+        <v>0.1431141528288641</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.03610126531222557</v>
+        <v>-0.05361658241145743</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.06492244284472433</v>
+        <v>-0.09128266807050919</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -5030,7 +5030,7 @@
         <v>-0</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -5039,106 +5039,106 @@
         <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>0.05176044398759182</v>
+        <v>0.01974838690814705</v>
       </c>
       <c r="U9" t="n">
         <v>-0</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.01296429472005033</v>
+        <v>-0.03481179621842266</v>
       </c>
       <c r="W9" t="n">
-        <v>0.04551309822433338</v>
+        <v>-0.01804110201377397</v>
       </c>
       <c r="X9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
         <v>-0</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA9" t="n">
         <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.07432588379896124</v>
+        <v>-0.01096127823676574</v>
       </c>
       <c r="AD9" t="n">
         <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>-0.02266366387756534</v>
+        <v>-0.05419236001869483</v>
       </c>
       <c r="AF9" t="n">
-        <v>-0.001224480753280984</v>
+        <v>-0.08401460815194697</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI9" t="n">
         <v>-0</v>
       </c>
       <c r="AJ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK9" t="n">
         <v>0</v>
       </c>
       <c r="AL9" t="n">
-        <v>-0.01395847238878522</v>
+        <v>0.08378448447434597</v>
       </c>
       <c r="AM9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN9" t="n">
-        <v>-0.01949573239197491</v>
+        <v>-0.03619475498582938</v>
       </c>
       <c r="AO9" t="n">
-        <v>-0.05075385585805868</v>
+        <v>0.03371713791799685</v>
       </c>
       <c r="AP9" t="n">
         <v>0</v>
       </c>
       <c r="AQ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR9" t="n">
         <v>-0</v>
       </c>
       <c r="AS9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AT9" t="n">
         <v>-0</v>
       </c>
       <c r="AU9" t="n">
-        <v>0.271105559606499</v>
+        <v>0.1638746154472801</v>
       </c>
       <c r="AV9" t="n">
         <v>-0</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.02716550267383306</v>
+        <v>-0.01902964100850176</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.05760547704500323</v>
+        <v>-0.118874275051047</v>
       </c>
       <c r="AY9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB9" t="n">
         <v>-0</v>
@@ -5147,25 +5147,25 @@
         <v>-0</v>
       </c>
       <c r="BD9" t="n">
-        <v>0.03512090807806188</v>
+        <v>-0.04487163654439904</v>
       </c>
       <c r="BE9" t="n">
         <v>0</v>
       </c>
       <c r="BF9" t="n">
-        <v>-0.06167631033570297</v>
+        <v>-0.03287449484047223</v>
       </c>
       <c r="BG9" t="n">
-        <v>-0.07148968657602472</v>
+        <v>-0.02936531392690681</v>
       </c>
       <c r="BH9" t="n">
         <v>0</v>
       </c>
       <c r="BI9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK9" t="n">
         <v>0</v>
@@ -5174,19 +5174,19 @@
         <v>-0</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.09564790629196808</v>
+        <v>0.03485947058212144</v>
       </c>
       <c r="BN9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO9" t="n">
-        <v>0.0245342303393524</v>
+        <v>0.03733060412200146</v>
       </c>
       <c r="BP9" t="n">
-        <v>0.09188926496735064</v>
+        <v>0.05332200704653858</v>
       </c>
       <c r="BQ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR9" t="n">
         <v>0</v>
@@ -5198,46 +5198,46 @@
         <v>-0</v>
       </c>
       <c r="BU9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BV9" t="n">
-        <v>0.1437524094562471</v>
+        <v>0.1199543368179821</v>
       </c>
       <c r="BW9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX9" t="n">
-        <v>0.02675378952602105</v>
+        <v>-0.05788556884541213</v>
       </c>
       <c r="BY9" t="n">
-        <v>0.032394988200355</v>
+        <v>-0.03248428353243221</v>
       </c>
       <c r="BZ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA9" t="n">
         <v>-0</v>
       </c>
       <c r="CB9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC9" t="n">
         <v>0</v>
       </c>
       <c r="CD9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CE9" t="n">
-        <v>-0.05417774189132009</v>
+        <v>-0.03980472244758285</v>
       </c>
       <c r="CF9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG9" t="n">
-        <v>-0.003497137250343219</v>
+        <v>0.04867789093999456</v>
       </c>
       <c r="CH9" t="n">
-        <v>0.004207604125726442</v>
+        <v>0.03167450285698527</v>
       </c>
       <c r="CI9" t="n">
         <v>-0</v>
@@ -5249,49 +5249,49 @@
         <v>0</v>
       </c>
       <c r="CL9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM9" t="n">
         <v>0</v>
       </c>
       <c r="CN9" t="n">
-        <v>-0.05053130129452643</v>
+        <v>-0.07722306170232424</v>
       </c>
       <c r="CO9" t="n">
         <v>-0</v>
       </c>
       <c r="CP9" t="n">
-        <v>-0.05117469884318675</v>
+        <v>0.0675631330833639</v>
       </c>
       <c r="CQ9" t="n">
-        <v>-0.06778434262476658</v>
+        <v>0.07768228389232389</v>
       </c>
       <c r="CR9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW9" t="n">
-        <v>-0.03443551391725058</v>
+        <v>-0.03569272112737672</v>
       </c>
       <c r="CX9" t="n">
         <v>-0</v>
       </c>
       <c r="CY9" t="n">
-        <v>0.01081715862233484</v>
+        <v>0.05640258921949039</v>
       </c>
       <c r="CZ9" t="n">
-        <v>-0.0009356902221457714</v>
+        <v>0.02889294106008697</v>
       </c>
       <c r="DA9" t="n">
         <v>0</v>
@@ -5300,7 +5300,7 @@
         <v>0</v>
       </c>
       <c r="DC9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD9" t="n">
         <v>0</v>
@@ -5309,22 +5309,22 @@
         <v>0</v>
       </c>
       <c r="DF9" t="n">
-        <v>-0.008774767323521407</v>
+        <v>-0.002031366856536744</v>
       </c>
       <c r="DG9" t="n">
         <v>0</v>
       </c>
       <c r="DH9" t="n">
-        <v>0.04934096845509875</v>
+        <v>0.001860540492744756</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.006959006331830516</v>
+        <v>-0.007888053567314261</v>
       </c>
       <c r="DJ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL9" t="n">
         <v>0</v>
@@ -5333,49 +5333,49 @@
         <v>0</v>
       </c>
       <c r="DN9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO9" t="n">
-        <v>-0.05481867880171114</v>
+        <v>-0.0473985064156719</v>
       </c>
       <c r="DP9" t="n">
         <v>0</v>
       </c>
       <c r="DQ9" t="n">
-        <v>0.01100052207401498</v>
+        <v>-0.01319462957483855</v>
       </c>
       <c r="DR9" t="n">
-        <v>-0.01960208134746441</v>
+        <v>-0.003201876125361723</v>
       </c>
       <c r="DS9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU9" t="n">
         <v>-0</v>
       </c>
       <c r="DV9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW9" t="n">
         <v>-0</v>
       </c>
       <c r="DX9" t="n">
-        <v>-0.0009595700095552714</v>
+        <v>0.0467002732391644</v>
       </c>
       <c r="DY9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ9" t="n">
-        <v>-0.008848658067557432</v>
+        <v>0.04543417021734147</v>
       </c>
       <c r="EA9" t="n">
-        <v>-0.02072811443456564</v>
+        <v>-0.02740175207168897</v>
       </c>
       <c r="EB9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC9" t="n">
         <v>0</v>
@@ -5384,22 +5384,22 @@
         <v>0</v>
       </c>
       <c r="EE9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EG9" t="n">
-        <v>-0.0292234452262134</v>
+        <v>-0.008174058928075356</v>
       </c>
       <c r="EH9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI9" t="n">
-        <v>0.003249620077032518</v>
+        <v>0.03805560307267736</v>
       </c>
       <c r="EJ9" t="n">
-        <v>0.05840912153465876</v>
+        <v>0.06648607814662416</v>
       </c>
       <c r="EK9" t="n">
         <v>-0</v>
@@ -5408,7 +5408,7 @@
         <v>-0</v>
       </c>
       <c r="EM9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN9" t="n">
         <v>-0</v>
@@ -5417,22 +5417,22 @@
         <v>0</v>
       </c>
       <c r="EP9" t="n">
-        <v>-0.03020410285874958</v>
+        <v>-0.01082951645956946</v>
       </c>
       <c r="EQ9" t="n">
         <v>0</v>
       </c>
       <c r="ER9" t="n">
-        <v>0.01393164283821401</v>
+        <v>0.05517179059981901</v>
       </c>
       <c r="ES9" t="n">
-        <v>0.02003740947964778</v>
+        <v>0.01083716446827314</v>
       </c>
       <c r="ET9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV9" t="n">
         <v>0</v>
@@ -5441,19 +5441,19 @@
         <v>-0</v>
       </c>
       <c r="EX9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EY9" t="n">
-        <v>-0.0338859263719237</v>
+        <v>-0.04765840038232711</v>
       </c>
       <c r="EZ9" t="n">
         <v>0</v>
       </c>
       <c r="FA9" t="n">
-        <v>0.004484970429474598</v>
+        <v>0.06055166043365363</v>
       </c>
       <c r="FB9" t="n">
-        <v>0.009783622604776965</v>
+        <v>0.02738361652416001</v>
       </c>
       <c r="FC9" t="n">
         <v>-0</v>
@@ -5468,19 +5468,19 @@
         <v>-0</v>
       </c>
       <c r="FG9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH9" t="n">
-        <v>0.01478795065603376</v>
+        <v>0.007000890477545102</v>
       </c>
       <c r="FI9" t="n">
         <v>-0</v>
       </c>
       <c r="FJ9" t="n">
-        <v>0.0209912384877548</v>
+        <v>0.0009698289548956687</v>
       </c>
       <c r="FK9" t="n">
-        <v>-0.03018620395461101</v>
+        <v>-0.024603696004661</v>
       </c>
       <c r="FL9" t="n">
         <v>-0</v>
@@ -5489,31 +5489,31 @@
         <v>-0</v>
       </c>
       <c r="FN9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ9" t="n">
-        <v>-0.03382237480022781</v>
+        <v>0.0100679411210021</v>
       </c>
       <c r="FR9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS9" t="n">
-        <v>-0.01811828423835254</v>
+        <v>0.03658741606999543</v>
       </c>
       <c r="FT9" t="n">
-        <v>0.005987955771124158</v>
+        <v>-0.06607595399739584</v>
       </c>
       <c r="FU9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FV9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FW9" t="n">
         <v>0</v>
@@ -5525,25 +5525,25 @@
         <v>-0</v>
       </c>
       <c r="FZ9" t="n">
-        <v>0.009702274871501488</v>
+        <v>-0.007045865373554557</v>
       </c>
       <c r="GA9" t="n">
         <v>-0</v>
       </c>
       <c r="GB9" t="n">
-        <v>-0.02519045122554731</v>
+        <v>0.02595064776670119</v>
       </c>
       <c r="GC9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE9" t="n">
         <v>-0</v>
       </c>
       <c r="GF9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG9" t="n">
         <v>-0</v>
@@ -5551,22 +5551,22 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="B10" t="n">
-        <v>0.2123120522139028</v>
+        <v>0.1912227681737327</v>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.01003017789952471</v>
+        <v>-0.1399156729220044</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.1346410759887489</v>
+        <v>-0.14401467555405</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -5578,37 +5578,37 @@
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K10" t="n">
-        <v>0.1612337751804058</v>
+        <v>0.4673042066353343</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.01876628031909322</v>
+        <v>-0.2012389135311907</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.1088497807581321</v>
+        <v>-0.1685358131111641</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
         <v>-0</v>
       </c>
       <c r="T10" t="n">
-        <v>0.01600919084274385</v>
+        <v>0.07924800543949265</v>
       </c>
       <c r="U10" t="n">
         <v>-0</v>
@@ -5617,37 +5617,37 @@
         <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.005310343219448102</v>
+        <v>-0.1018786887130419</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.003379788542237069</v>
+        <v>-0.02193531168851543</v>
       </c>
       <c r="Y10" t="n">
         <v>-0</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB10" t="n">
         <v>-0</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.02264195369145238</v>
+        <v>-0.03422258620817783</v>
       </c>
       <c r="AD10" t="n">
         <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.01307762758295742</v>
+        <v>-0.2488385414720703</v>
       </c>
       <c r="AG10" t="n">
-        <v>-0.005140299831561942</v>
+        <v>-0.03436988946435927</v>
       </c>
       <c r="AH10" t="n">
         <v>-0</v>
@@ -5659,10 +5659,10 @@
         <v>-0</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL10" t="n">
-        <v>0.009900918702396332</v>
+        <v>0.02833008496973151</v>
       </c>
       <c r="AM10" t="n">
         <v>-0</v>
@@ -5671,13 +5671,13 @@
         <v>0</v>
       </c>
       <c r="AO10" t="n">
-        <v>-0.01505912141223688</v>
+        <v>-0.05337306341343624</v>
       </c>
       <c r="AP10" t="n">
-        <v>-0.03623837143679418</v>
+        <v>-0.02173792955855149</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR10" t="n">
         <v>-0</v>
@@ -5689,34 +5689,34 @@
         <v>-0</v>
       </c>
       <c r="AU10" t="n">
-        <v>0.1351779647404379</v>
+        <v>0.4881765105994598</v>
       </c>
       <c r="AV10" t="n">
         <v>-0</v>
       </c>
       <c r="AW10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AX10" t="n">
-        <v>0.0007187053930370897</v>
+        <v>-0.162984894241908</v>
       </c>
       <c r="AY10" t="n">
-        <v>-0.06373899951584794</v>
+        <v>-0.1619159427409604</v>
       </c>
       <c r="AZ10" t="n">
         <v>0</v>
       </c>
       <c r="BA10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB10" t="n">
         <v>0</v>
       </c>
       <c r="BC10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD10" t="n">
-        <v>0.06111520225086265</v>
+        <v>-0.1255381939011536</v>
       </c>
       <c r="BE10" t="n">
         <v>0</v>
@@ -5725,40 +5725,40 @@
         <v>0</v>
       </c>
       <c r="BG10" t="n">
-        <v>-0.03887965167650223</v>
+        <v>-0.1331298720800951</v>
       </c>
       <c r="BH10" t="n">
-        <v>-0.05265046515155046</v>
+        <v>0.006650183597233844</v>
       </c>
       <c r="BI10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK10" t="n">
         <v>-0</v>
       </c>
       <c r="BL10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.05448905437334829</v>
+        <v>0.1657753252549579</v>
       </c>
       <c r="BN10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO10" t="n">
         <v>-0</v>
       </c>
       <c r="BP10" t="n">
-        <v>0.03628360773034428</v>
+        <v>0.1011413597745587</v>
       </c>
       <c r="BQ10" t="n">
-        <v>0.006212551462032995</v>
+        <v>-0.003060126952359992</v>
       </c>
       <c r="BR10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS10" t="n">
         <v>-0</v>
@@ -5770,88 +5770,88 @@
         <v>-0</v>
       </c>
       <c r="BV10" t="n">
-        <v>0.06201278847516619</v>
+        <v>0.2957878599855076</v>
       </c>
       <c r="BW10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX10" t="n">
         <v>0</v>
       </c>
       <c r="BY10" t="n">
-        <v>-0.009151302790195022</v>
+        <v>-0.0963027287433225</v>
       </c>
       <c r="BZ10" t="n">
-        <v>-0.01674553713005551</v>
+        <v>-0.05097128639500731</v>
       </c>
       <c r="CA10" t="n">
         <v>-0</v>
       </c>
       <c r="CB10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CD10" t="n">
         <v>-0</v>
       </c>
       <c r="CE10" t="n">
-        <v>-0.03539821625749956</v>
+        <v>-0.05875008752663604</v>
       </c>
       <c r="CF10" t="n">
         <v>0</v>
       </c>
       <c r="CG10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CH10" t="n">
-        <v>-0.004182445543096932</v>
+        <v>0.0861337879755396</v>
       </c>
       <c r="CI10" t="n">
-        <v>0.02853942149898875</v>
+        <v>0.05833526882708124</v>
       </c>
       <c r="CJ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK10" t="n">
         <v>0</v>
       </c>
       <c r="CL10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM10" t="n">
         <v>0</v>
       </c>
       <c r="CN10" t="n">
-        <v>-0.02078043351665047</v>
+        <v>-0.2612232928029988</v>
       </c>
       <c r="CO10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ10" t="n">
-        <v>0.01497758490643686</v>
+        <v>0.2107801161442127</v>
       </c>
       <c r="CR10" t="n">
-        <v>-0.01727191803191523</v>
+        <v>0.07031189033057132</v>
       </c>
       <c r="CS10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT10" t="n">
         <v>-0</v>
       </c>
       <c r="CU10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW10" t="n">
-        <v>-0.02434196462158215</v>
+        <v>-0.05193979238003965</v>
       </c>
       <c r="CX10" t="n">
         <v>-0</v>
@@ -5860,106 +5860,106 @@
         <v>0</v>
       </c>
       <c r="CZ10" t="n">
-        <v>-0.003695217839293305</v>
+        <v>0.05831981683059068</v>
       </c>
       <c r="DA10" t="n">
-        <v>0.02659503796763685</v>
+        <v>0.06647500373464019</v>
       </c>
       <c r="DB10" t="n">
         <v>0</v>
       </c>
       <c r="DC10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DD10" t="n">
         <v>0</v>
       </c>
       <c r="DE10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DF10" t="n">
-        <v>-0.01164207611249794</v>
+        <v>0.01976561903150227</v>
       </c>
       <c r="DG10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI10" t="n">
-        <v>0.002407800722476405</v>
+        <v>-0.02437734242421425</v>
       </c>
       <c r="DJ10" t="n">
-        <v>0.005262283053697603</v>
+        <v>-0.009090610337942505</v>
       </c>
       <c r="DK10" t="n">
         <v>0</v>
       </c>
       <c r="DL10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DM10" t="n">
         <v>0</v>
       </c>
       <c r="DN10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO10" t="n">
-        <v>-0.01925715766589115</v>
+        <v>-0.1012552686040837</v>
       </c>
       <c r="DP10" t="n">
         <v>0</v>
       </c>
       <c r="DQ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR10" t="n">
-        <v>0.003330711197191196</v>
+        <v>0.09753901312548169</v>
       </c>
       <c r="DS10" t="n">
-        <v>-0.002264847878490785</v>
+        <v>0.03026381919603685</v>
       </c>
       <c r="DT10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU10" t="n">
         <v>-0</v>
       </c>
       <c r="DV10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW10" t="n">
         <v>-0</v>
       </c>
       <c r="DX10" t="n">
-        <v>0.004988839601625447</v>
+        <v>0.05198302220295879</v>
       </c>
       <c r="DY10" t="n">
         <v>0</v>
       </c>
       <c r="DZ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EA10" t="n">
-        <v>-0.01747647285040631</v>
+        <v>-0.04007143507805237</v>
       </c>
       <c r="EB10" t="n">
-        <v>-0.007420395838533121</v>
+        <v>-0.0593206821148895</v>
       </c>
       <c r="EC10" t="n">
         <v>-0</v>
       </c>
       <c r="ED10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG10" t="n">
-        <v>-0.01881876497743303</v>
+        <v>0.04645593637210518</v>
       </c>
       <c r="EH10" t="n">
         <v>0</v>
@@ -5968,25 +5968,25 @@
         <v>0</v>
       </c>
       <c r="EJ10" t="n">
-        <v>0.009901489105061544</v>
+        <v>0.0219868673912284</v>
       </c>
       <c r="EK10" t="n">
-        <v>0.01657321828088137</v>
+        <v>0.04208644450518873</v>
       </c>
       <c r="EL10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM10" t="n">
         <v>-0</v>
       </c>
       <c r="EN10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO10" t="n">
         <v>0</v>
       </c>
       <c r="EP10" t="n">
-        <v>-0.01700140065530764</v>
+        <v>0.02310383875618978</v>
       </c>
       <c r="EQ10" t="n">
         <v>0</v>
@@ -5995,10 +5995,10 @@
         <v>-0</v>
       </c>
       <c r="ES10" t="n">
-        <v>-0.0031276441474826</v>
+        <v>-0.01722211773790573</v>
       </c>
       <c r="ET10" t="n">
-        <v>0.03223568669671888</v>
+        <v>0.03739425406422568</v>
       </c>
       <c r="EU10" t="n">
         <v>-0</v>
@@ -6007,13 +6007,13 @@
         <v>0</v>
       </c>
       <c r="EW10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX10" t="n">
         <v>-0</v>
       </c>
       <c r="EY10" t="n">
-        <v>-0.02616596934814044</v>
+        <v>-0.06781422926840877</v>
       </c>
       <c r="EZ10" t="n">
         <v>0</v>
@@ -6022,25 +6022,25 @@
         <v>-0</v>
       </c>
       <c r="FB10" t="n">
-        <v>0.00164303499632516</v>
+        <v>0.05735946287526131</v>
       </c>
       <c r="FC10" t="n">
-        <v>0.02947926088353579</v>
+        <v>0.06653959294237094</v>
       </c>
       <c r="FD10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE10" t="n">
         <v>0</v>
       </c>
       <c r="FF10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG10" t="n">
         <v>0</v>
       </c>
       <c r="FH10" t="n">
-        <v>-0.005738043375841332</v>
+        <v>-0.02518727153646741</v>
       </c>
       <c r="FI10" t="n">
         <v>-0</v>
@@ -6049,52 +6049,52 @@
         <v>-0</v>
       </c>
       <c r="FK10" t="n">
-        <v>-0.01844380813070224</v>
+        <v>0.04595135175888836</v>
       </c>
       <c r="FL10" t="n">
-        <v>0.01906306640265226</v>
+        <v>0.01110702667291558</v>
       </c>
       <c r="FM10" t="n">
         <v>0</v>
       </c>
       <c r="FN10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ10" t="n">
-        <v>-0.008517532145450566</v>
+        <v>-0.05497613162861437</v>
       </c>
       <c r="FR10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FT10" t="n">
-        <v>-0.02990831916245438</v>
+        <v>-0.1063963044628545</v>
       </c>
       <c r="FU10" t="n">
-        <v>0.001171938700577602</v>
+        <v>0.008222917780106606</v>
       </c>
       <c r="FV10" t="n">
         <v>-0</v>
       </c>
       <c r="FW10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY10" t="n">
         <v>-0</v>
       </c>
       <c r="FZ10" t="n">
-        <v>-0.02106424956061611</v>
+        <v>-0.0006404823739502553</v>
       </c>
       <c r="GA10" t="n">
         <v>-0</v>
@@ -6106,7 +6106,7 @@
         <v>0</v>
       </c>
       <c r="GD10" t="n">
-        <v>-0.02431711647482723</v>
+        <v>-0.01113862998798352</v>
       </c>
       <c r="GE10" t="n">
         <v>-0</v>
@@ -6115,7 +6115,7 @@
         <v>-0</v>
       </c>
       <c r="GG10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
